--- a/03-Testing/UAT-files/TC-026_ecr-other-section.xlsx
+++ b/03-Testing/UAT-files/TC-026_ecr-other-section.xlsx
@@ -148,10 +148,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -183,10 +183,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -467,7 +467,7 @@
         <v>SCHOOL YEAR</v>
       </c>
       <c r="Y5" t="str">
-        <v>2026-2027</v>
+        <v>2025-2026</v>
       </c>
     </row>
     <row r="7">
@@ -475,19 +475,19 @@
         <v xml:space="preserve">GRADE &amp; SECTION: </v>
       </c>
       <c r="J7" t="str">
-        <v>Grade 4 - Mabini</v>
+        <v>Grade 3 - Mabini</v>
       </c>
       <c r="N7" t="str">
         <v>TEACHER:</v>
       </c>
       <c r="Q7" t="str">
-        <v>Maria Elena Santos</v>
+        <v>Mabini Teacher</v>
       </c>
       <c r="W7" t="str">
         <v>SUBJECT:</v>
       </c>
       <c r="Y7" t="str">
-        <v>English</v>
+        <v>Mathematics</v>
       </c>
     </row>
     <row r="8">
